--- a/UGANDA/UGANDA EXPENSES APRIL-2026.xlsx
+++ b/UGANDA/UGANDA EXPENSES APRIL-2026.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sale  and weekly report\Uganda\April for razy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\pc\dashboards\uganda-sales-dashboard\UGANDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47B52AB-B5D1-4330-8B3B-21C487E4AE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{2970B40F-7A49-4858-8CF7-55AAD769FA10}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18810" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="MONEY REVEIVED" sheetId="1" r:id="rId1"/>
     <sheet name="ACTIVITY EXPENSES" sheetId="2" r:id="rId2"/>
     <sheet name="Other EXP" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -115,9 +114,6 @@
     <t>JULIUS</t>
   </si>
   <si>
-    <t>MOSES MPIUS</t>
-  </si>
-  <si>
     <t>MASEREKA ASANSIO</t>
   </si>
   <si>
@@ -244,12 +240,15 @@
   </si>
   <si>
     <t>Motivation</t>
+  </si>
+  <si>
+    <t>MOSES EPIUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -498,6 +497,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -505,13 +507,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{4E013470-1A1F-46E2-A9B2-0485950C9185}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -822,7 +821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F0E6DB-7860-460B-9367-91CF31A856CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -833,14 +832,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -853,10 +852,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>4</v>
@@ -899,7 +898,7 @@
         <v>46142</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" s="25">
         <f>E5*3500</f>
@@ -918,7 +917,7 @@
         <v>46142</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="25">
         <f>E6*3500</f>
@@ -935,7 +934,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="A3:A6" xr:uid="{D346F336-5264-4D76-B72B-901DD2951E83}">
+    <dataValidation type="list" sqref="A3:A6">
       <formula1>"OPENING BALANCE,RECEIVED,SPENT,BALANCE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -944,7 +943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB1DF55-5B11-4DAC-B5D1-4B73C5F5A60E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -962,40 +961,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>14</v>
@@ -1018,16 +1017,16 @@
         <v>22</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>68</v>
+        <v>31</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" s="21">
         <v>43.142857142857146</v>
@@ -1036,7 +1035,7 @@
         <v>77653457</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="3">
         <v>466</v>
@@ -1053,23 +1052,23 @@
         <v>23</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>68</v>
+        <v>32</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" s="19">
         <v>71.714285714285708</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J4" s="3">
         <v>3000</v>
@@ -1086,23 +1085,23 @@
         <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>68</v>
+        <v>31</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" s="19">
         <v>42.857142857142854</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J5" s="3">
         <v>407</v>
@@ -1119,23 +1118,23 @@
         <v>25</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="G6" s="21">
         <v>15</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J6" s="3">
         <v>1500</v>
@@ -1149,26 +1148,26 @@
         <v>5</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>68</v>
+        <v>34</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" s="26">
         <v>14.285714285714286</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -1182,26 +1181,26 @@
         <v>6</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>68</v>
+        <v>34</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="21">
         <v>5.7142857142857144</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -1215,26 +1214,26 @@
         <v>7</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="G9" s="19">
         <v>28.857142857142858</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -1248,26 +1247,26 @@
         <v>8</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>68</v>
+        <v>32</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10" s="19">
         <v>60.285714285714285</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -1281,26 +1280,26 @@
         <v>9</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>68</v>
+        <v>33</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="19">
         <v>8.7142857142857135</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J11" s="3">
         <v>703.97</v>
@@ -1314,26 +1313,26 @@
         <v>10</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>68</v>
+        <v>34</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" s="19">
         <v>14.428571428571429</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -1652,7 +1651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7523D74-5E62-41DF-9E48-B9E76BDE414F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1662,15 +1661,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="A1" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -1683,10 +1682,10 @@
         <v>19</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>20</v>
@@ -1700,17 +1699,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="19">
         <v>142</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3"/>
     </row>
@@ -1719,17 +1718,17 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="19">
         <v>86.46</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3"/>
     </row>
